--- a/Разное/Объекты для базы данных.xlsx
+++ b/Разное/Объекты для базы данных.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ЭтаКнига"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvg\Desktop\Работа по базе данных автохим\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pvg\Documents\GitHub\AUTO-GEN-FINAL-VERSION\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBF58285-04DA-43DA-86B1-612DB27E5371}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{050959A8-EA7D-46DE-97E2-C4D7F796E645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Готовые объекты" sheetId="4" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Готовые объекты'!$A$1:$L$361</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Готовые объекты'!$A$1:$L$458</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
